--- a/data/pronostici/TOTOMONDIALE2026_Domenico_Grimaldi.xlsx
+++ b/data/pronostici/TOTOMONDIALE2026_Domenico_Grimaldi.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr hidePivotFieldList="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\e.castiello\Documents\totomondiale\data\pronostici\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F116C86C-D5C9-4FA9-9840-3A68D8F829EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15510" windowHeight="6170" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="REGOLAMENTO" sheetId="1" r:id="rId1"/>
@@ -24,23 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="288">
   <si>
     <t>REGOLAMENTO</t>
   </si>
@@ -642,9 +632,6 @@
     <t>x</t>
   </si>
   <si>
-    <t>1 1</t>
-  </si>
-  <si>
     <t>Schick</t>
   </si>
   <si>
@@ -663,9 +650,6 @@
     <t>Rapinha</t>
   </si>
   <si>
-    <t>2 2</t>
-  </si>
-  <si>
     <t>0-3</t>
   </si>
   <si>
@@ -693,9 +677,6 @@
     <t>Gyökeres</t>
   </si>
   <si>
-    <t>2 1</t>
-  </si>
-  <si>
     <t>5-0</t>
   </si>
   <si>
@@ -705,9 +686,6 @@
     <t>Salah</t>
   </si>
   <si>
-    <t>1 2</t>
-  </si>
-  <si>
     <t>Valverde</t>
   </si>
   <si>
@@ -732,9 +710,6 @@
     <t>Ronado C.</t>
   </si>
   <si>
-    <t xml:space="preserve">2-0 </t>
-  </si>
-  <si>
     <t>Kane</t>
   </si>
   <si>
@@ -771,9 +746,6 @@
     <t>Pulisic</t>
   </si>
   <si>
-    <t xml:space="preserve">2 2 </t>
-  </si>
-  <si>
     <t>McTominay</t>
   </si>
   <si>
@@ -813,15 +785,9 @@
     <t>Dembele</t>
   </si>
   <si>
-    <t>0 1</t>
-  </si>
-  <si>
     <t>Amoura</t>
   </si>
   <si>
-    <t>2.0</t>
-  </si>
-  <si>
     <t>Bruno Fernandes</t>
   </si>
   <si>
@@ -837,12 +803,6 @@
     <t>Domenico</t>
   </si>
   <si>
-    <t>3 1</t>
-  </si>
-  <si>
-    <t>1 3</t>
-  </si>
-  <si>
     <t>dani olmo</t>
   </si>
   <si>
@@ -913,12 +873,33 @@
   </si>
   <si>
     <t>SPAGNA</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-2 </t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -1418,7 +1399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1439,13 +1420,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -1486,11 +1461,161 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1504,7 +1629,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1519,163 +1644,13 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1696,7 +1671,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Albricci Francesco" refreshedDate="46167.475645949075" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Albricci Francesco" refreshedDate="46167.475645949075" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="48" xr:uid="{00000000-000A-0000-FFFF-FFFF00000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:A48" sheet="Gironi"/>
   </cacheSource>
@@ -1976,7 +1951,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000000000000}" name="Tabella pivot2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valori" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A2:A63" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
@@ -2550,7 +2525,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
@@ -2559,247 +2534,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="44"/>
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="71"/>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37" t="s">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="38"/>
+      <c r="F3" s="64"/>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37" t="s">
+      <c r="B4" s="63"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="38"/>
+      <c r="F4" s="64"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="36" t="s">
+      <c r="A5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="63"/>
+      <c r="D5" s="63"/>
+      <c r="E5" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="38"/>
+      <c r="F5" s="64"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="39"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="41"/>
+      <c r="A6" s="72"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="74"/>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37" t="s">
+      <c r="B7" s="63"/>
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="38"/>
+      <c r="F7" s="64"/>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="36" t="s">
+      <c r="A8" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37" t="s">
+      <c r="B8" s="63"/>
+      <c r="C8" s="63"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="38"/>
+      <c r="F8" s="64"/>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37" t="s">
+      <c r="B9" s="63"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="38"/>
+      <c r="F9" s="64"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="39"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="41"/>
+      <c r="A10" s="72"/>
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="74"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="37"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37" t="s">
+      <c r="B11" s="63"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="38"/>
+      <c r="F11" s="64"/>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37" t="s">
+      <c r="B12" s="63"/>
+      <c r="C12" s="63"/>
+      <c r="D12" s="63"/>
+      <c r="E12" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="38"/>
+      <c r="F12" s="64"/>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B13" s="37"/>
-      <c r="C13" s="37"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37" t="s">
+      <c r="B13" s="63"/>
+      <c r="C13" s="63"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="38"/>
+      <c r="F13" s="64"/>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="39"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="41"/>
+      <c r="A14" s="72"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="74"/>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="36" t="s">
+      <c r="A15" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37" t="s">
+      <c r="B15" s="63"/>
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="38"/>
+      <c r="F15" s="64"/>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="36" t="s">
+      <c r="A16" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37" t="s">
+      <c r="B16" s="63"/>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="38"/>
+      <c r="F16" s="64"/>
     </row>
     <row r="17" spans="1:6">
-      <c r="A17" s="36" t="s">
+      <c r="A17" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37" t="s">
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="38"/>
+      <c r="F17" s="64"/>
     </row>
     <row r="18" spans="1:6">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37" t="s">
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="38"/>
+      <c r="F18" s="64"/>
     </row>
     <row r="19" spans="1:6">
-      <c r="A19" s="36" t="s">
+      <c r="A19" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37" t="s">
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="F19" s="38"/>
+      <c r="F19" s="64"/>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="75" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="29"/>
+      <c r="B20" s="76"/>
+      <c r="C20" s="76"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="1:6">
-      <c r="A21" s="30"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
+      <c r="A21" s="78"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="79"/>
+      <c r="D21" s="79"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="80"/>
     </row>
     <row r="22" spans="1:6" ht="14.5" thickBot="1">
-      <c r="A22" s="33"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="35"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="82"/>
+      <c r="F22" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A20:F22"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A4:D4"/>
@@ -2809,39 +2810,13 @@
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="A20:F22"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:T82"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5"/>
   <cols>
@@ -2857,2070 +2832,2185 @@
   <sheetData>
     <row r="1" spans="1:20" ht="16.5" customHeight="1"/>
     <row r="2" spans="1:20">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="58" t="s">
-        <v>264</v>
-      </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
     </row>
     <row r="3" spans="1:20">
-      <c r="A3" s="57" t="s">
+      <c r="A3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="58" t="s">
-        <v>263</v>
+      <c r="B3" s="58"/>
+      <c r="C3" s="32" t="s">
+        <v>255</v>
       </c>
       <c r="D3" s="59"/>
       <c r="E3" s="59"/>
       <c r="F3" s="59"/>
     </row>
     <row r="5" spans="1:20">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="80"/>
-      <c r="P5" s="80"/>
-      <c r="Q5" s="80"/>
-      <c r="R5" s="80"/>
-      <c r="S5" s="80"/>
-      <c r="T5" s="80"/>
+      <c r="B5" s="23"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="23"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="23"/>
+      <c r="S5" s="23"/>
+      <c r="T5" s="23"/>
     </row>
     <row r="6" spans="1:20" ht="15" thickBot="1">
-      <c r="A6" s="80"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="80"/>
-      <c r="L6" s="80"/>
-      <c r="M6" s="80"/>
-      <c r="N6" s="80"/>
-      <c r="O6" s="80"/>
-      <c r="P6" s="80"/>
-      <c r="Q6" s="80"/>
-      <c r="R6" s="80"/>
-      <c r="S6" s="80"/>
-      <c r="T6" s="80"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="23"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+      <c r="L6" s="23"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="23"/>
+      <c r="P6" s="23"/>
+      <c r="Q6" s="23"/>
+      <c r="R6" s="23"/>
+      <c r="S6" s="23"/>
+      <c r="T6" s="23"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1">
-      <c r="A7" s="85" t="s">
+      <c r="A7" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
-      <c r="G7" s="86"/>
-      <c r="H7" s="87"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="85" t="s">
+      <c r="J7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="K7" s="86"/>
-      <c r="L7" s="86"/>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
-      <c r="Q7" s="87"/>
+      <c r="K7" s="29"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="29"/>
+      <c r="N7" s="29"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="30"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
       <c r="T7" s="1"/>
     </row>
     <row r="8" spans="1:20" ht="18.5">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="13" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="81" t="s">
+      <c r="C8" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
       <c r="F8" s="4" t="s">
         <v>35</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="82" t="s">
+      <c r="J8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="84"/>
+      <c r="K8" s="26"/>
+      <c r="L8" s="26"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="26"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="27"/>
     </row>
     <row r="9" spans="1:20" ht="18.5">
-      <c r="A9" s="17">
+      <c r="A9" s="15">
         <v>46184</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="49"/>
-      <c r="E9" s="50"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="37"/>
       <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="J9" s="82" t="s">
+      <c r="J9" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83" t="s">
+      <c r="K9" s="26"/>
+      <c r="L9" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83" t="s">
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="84"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="27"/>
     </row>
     <row r="10" spans="1:20">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <v>46185</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="52"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="9" t="s">
+      <c r="D10" s="39"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="H10" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="J10" s="60" t="s">
+      <c r="J10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="K10" s="58"/>
-      <c r="L10" s="61" t="s">
+      <c r="K10" s="32"/>
+      <c r="L10" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="M10" s="61"/>
-      <c r="N10" s="61"/>
-      <c r="O10" s="61" t="s">
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="P10" s="61"/>
-      <c r="Q10" s="62"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="34"/>
     </row>
     <row r="11" spans="1:20">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <v>46185</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="52"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="9" t="s">
+      <c r="D11" s="39"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>241</v>
-      </c>
-      <c r="J11" s="60" t="s">
+      <c r="G11" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="K11" s="58"/>
-      <c r="L11" s="61" t="s">
+      <c r="K11" s="32"/>
+      <c r="L11" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="M11" s="61"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="61" t="s">
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="62"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="34"/>
     </row>
     <row r="12" spans="1:20">
-      <c r="A12" s="17">
+      <c r="A12" s="15">
         <v>46186</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="50"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="7">
         <v>1</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="J12" s="60" t="s">
+      <c r="H12" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="J12" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="K12" s="58"/>
-      <c r="L12" s="61" t="s">
+      <c r="K12" s="32"/>
+      <c r="L12" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61" t="s">
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="P12" s="61"/>
-      <c r="Q12" s="62"/>
+      <c r="P12" s="33"/>
+      <c r="Q12" s="34"/>
     </row>
     <row r="13" spans="1:20">
-      <c r="A13" s="17">
+      <c r="A13" s="15">
         <v>46186</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="37"/>
       <c r="F13" s="7">
         <v>2</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="84" t="s">
+        <v>202</v>
+      </c>
+      <c r="H13" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="J13" s="60" t="s">
+      <c r="J13" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="K13" s="58"/>
-      <c r="L13" s="61" t="s">
+      <c r="K13" s="32"/>
+      <c r="L13" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="M13" s="61"/>
-      <c r="N13" s="61"/>
-      <c r="O13" s="61" t="s">
-        <v>234</v>
-      </c>
-      <c r="P13" s="61"/>
-      <c r="Q13" s="62"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="33" t="s">
+        <v>229</v>
+      </c>
+      <c r="P13" s="33"/>
+      <c r="Q13" s="34"/>
     </row>
     <row r="14" spans="1:20">
-      <c r="A14" s="19">
+      <c r="A14" s="17">
         <v>46187</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="9">
+      <c r="D14" s="39"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="8">
         <v>1</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="H14" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="H14" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="J14" s="60" t="s">
+      <c r="J14" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="K14" s="58"/>
-      <c r="L14" s="61" t="s">
+      <c r="K14" s="32"/>
+      <c r="L14" s="33" t="s">
         <v>179</v>
       </c>
-      <c r="M14" s="61"/>
-      <c r="N14" s="61"/>
-      <c r="O14" s="61" t="s">
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="62"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="34"/>
     </row>
     <row r="15" spans="1:20">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <v>46187</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="51" t="s">
+      <c r="C15" s="38" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="9">
+      <c r="D15" s="39"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="8">
         <v>2</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="J15" s="60" t="s">
+      <c r="G15" s="85" t="s">
+        <v>206</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="J15" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="K15" s="58"/>
-      <c r="L15" s="61" t="s">
+      <c r="K15" s="32"/>
+      <c r="L15" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61" t="s">
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="P15" s="61"/>
-      <c r="Q15" s="62"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="34"/>
     </row>
     <row r="16" spans="1:20">
-      <c r="A16" s="19">
+      <c r="A16" s="17">
         <v>46187</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="38" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="52"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="9">
+      <c r="D16" s="39"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="8">
         <v>2</v>
       </c>
-      <c r="G16" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="J16" s="60" t="s">
+      <c r="G16" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="H16" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="J16" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="58"/>
-      <c r="L16" s="61" t="s">
+      <c r="K16" s="32"/>
+      <c r="L16" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="M16" s="61"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="61" t="s">
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="P16" s="61"/>
-      <c r="Q16" s="62"/>
+      <c r="P16" s="33"/>
+      <c r="Q16" s="34"/>
     </row>
     <row r="17" spans="1:17">
-      <c r="A17" s="19">
+      <c r="A17" s="17">
         <v>46187</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="51" t="s">
+      <c r="C17" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="52"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="9">
+      <c r="D17" s="39"/>
+      <c r="E17" s="40"/>
+      <c r="F17" s="8">
         <v>1</v>
       </c>
-      <c r="G17" s="10" t="s">
-        <v>213</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="J17" s="60" t="s">
+      <c r="G17" s="85" t="s">
+        <v>211</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="J17" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="K17" s="58"/>
-      <c r="L17" s="61" t="s">
+      <c r="K17" s="32"/>
+      <c r="L17" s="33" t="s">
         <v>188</v>
       </c>
-      <c r="M17" s="61"/>
-      <c r="N17" s="61"/>
-      <c r="O17" s="61" t="s">
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33" t="s">
         <v>152</v>
       </c>
-      <c r="P17" s="61"/>
-      <c r="Q17" s="62"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="34"/>
     </row>
     <row r="18" spans="1:17">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <v>46187</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C18" s="51" t="s">
+      <c r="C18" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="52"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="9" t="s">
+      <c r="D18" s="39"/>
+      <c r="E18" s="40"/>
+      <c r="F18" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="G18" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="J18" s="60" t="s">
+      <c r="G18" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="H18" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="J18" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="K18" s="58"/>
-      <c r="L18" s="61" t="s">
+      <c r="K18" s="32"/>
+      <c r="L18" s="33" t="s">
         <v>190</v>
       </c>
-      <c r="M18" s="61"/>
-      <c r="N18" s="61"/>
-      <c r="O18" s="61" t="s">
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="33" t="s">
         <v>191</v>
       </c>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="62"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="34"/>
     </row>
     <row r="19" spans="1:17">
-      <c r="A19" s="17">
+      <c r="A19" s="15">
         <v>46188</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="49"/>
-      <c r="E19" s="50"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="37"/>
       <c r="F19" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G19" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="H19" s="18" t="s">
-        <v>215</v>
-      </c>
-      <c r="J19" s="60" t="s">
+      <c r="G19" s="84" t="s">
+        <v>202</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="J19" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="K19" s="58"/>
-      <c r="L19" s="61" t="s">
+      <c r="K19" s="32"/>
+      <c r="L19" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="M19" s="61"/>
-      <c r="N19" s="61"/>
-      <c r="O19" s="61" t="s">
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="62"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="34"/>
     </row>
     <row r="20" spans="1:17">
-      <c r="A20" s="17">
+      <c r="A20" s="15">
         <v>46188</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="50"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="37"/>
       <c r="F20" s="7">
         <v>1</v>
       </c>
-      <c r="G20" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H20" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="J20" s="60" t="s">
+      <c r="G20" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="J20" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="K20" s="58"/>
-      <c r="L20" s="61" t="s">
+      <c r="K20" s="32"/>
+      <c r="L20" s="33" t="s">
         <v>193</v>
       </c>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61" t="s">
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="62"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="34"/>
     </row>
     <row r="21" spans="1:17" ht="15" thickBot="1">
-      <c r="A21" s="17">
+      <c r="A21" s="15">
         <v>46188</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="48" t="s">
+      <c r="C21" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D21" s="49"/>
-      <c r="E21" s="50"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="37"/>
       <c r="F21" s="7">
         <v>1</v>
       </c>
-      <c r="G21" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="H21" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="J21" s="78" t="s">
+      <c r="G21" s="84" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="J21" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="K21" s="79"/>
-      <c r="L21" s="64" t="s">
+      <c r="K21" s="44"/>
+      <c r="L21" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64" t="s">
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="42"/>
     </row>
     <row r="22" spans="1:17" ht="15" thickBot="1">
-      <c r="A22" s="17">
+      <c r="A22" s="15">
         <v>46188</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="35" t="s">
         <v>66</v>
       </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="50"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="37"/>
       <c r="F22" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G22" s="26" t="s">
-        <v>221</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>220</v>
+      <c r="G22" s="84" t="s">
+        <v>284</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="18.5">
-      <c r="A23" s="19">
+      <c r="A23" s="17">
         <v>46189</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="51" t="s">
+      <c r="C23" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="D23" s="52"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="9">
+      <c r="D23" s="39"/>
+      <c r="E23" s="40"/>
+      <c r="F23" s="8">
         <v>2</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="L23" s="66" t="s">
+      <c r="G23" s="85" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="L23" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
+      <c r="M23" s="46"/>
+      <c r="N23" s="46"/>
+      <c r="O23" s="46"/>
+      <c r="P23" s="47"/>
     </row>
     <row r="24" spans="1:17">
-      <c r="A24" s="19">
+      <c r="A24" s="17">
         <v>46189</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C24" s="51" t="s">
+      <c r="C24" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="52"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="9">
+      <c r="D24" s="39"/>
+      <c r="E24" s="40"/>
+      <c r="F24" s="8">
         <v>2</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H24" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="L24" s="60" t="s">
-        <v>289</v>
-      </c>
-      <c r="M24" s="61"/>
-      <c r="N24" s="61"/>
-      <c r="O24" s="61"/>
-      <c r="P24" s="62"/>
+      <c r="G24" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="L24" s="31" t="s">
+        <v>279</v>
+      </c>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="34"/>
     </row>
     <row r="25" spans="1:17" ht="15" thickBot="1">
-      <c r="A25" s="19">
+      <c r="A25" s="17">
         <v>46189</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="51" t="s">
+      <c r="C25" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="52"/>
-      <c r="E25" s="53"/>
-      <c r="F25" s="9">
+      <c r="D25" s="39"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="8">
         <v>1</v>
       </c>
-      <c r="G25" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="L25" s="63"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="64"/>
-      <c r="P25" s="65"/>
+      <c r="G25" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H25" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="L25" s="48"/>
+      <c r="M25" s="41"/>
+      <c r="N25" s="41"/>
+      <c r="O25" s="41"/>
+      <c r="P25" s="42"/>
     </row>
     <row r="26" spans="1:17" ht="15" thickBot="1">
-      <c r="A26" s="17">
+      <c r="A26" s="15">
         <v>46190</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="50"/>
+      <c r="D26" s="36"/>
+      <c r="E26" s="37"/>
       <c r="F26" s="7">
         <v>2</v>
       </c>
-      <c r="G26" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H26" s="18" t="s">
-        <v>226</v>
+      <c r="G26" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="18.5">
-      <c r="A27" s="17">
+      <c r="A27" s="15">
         <v>46190</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="35" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="49"/>
-      <c r="E27" s="50"/>
+      <c r="D27" s="36"/>
+      <c r="E27" s="37"/>
       <c r="F27" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G27" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H27" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="L27" s="75" t="s">
+      <c r="G27" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="L27" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="M27" s="76"/>
-      <c r="N27" s="76"/>
-      <c r="O27" s="76"/>
-      <c r="P27" s="77"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="51"/>
     </row>
     <row r="28" spans="1:17">
-      <c r="A28" s="17">
+      <c r="A28" s="15">
         <v>46190</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="50"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="37"/>
       <c r="F28" s="7">
         <v>1</v>
       </c>
-      <c r="G28" s="8" t="s">
+      <c r="G28" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="L28" s="60" t="s">
+      <c r="H28" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="L28" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="58" t="s">
-        <v>289</v>
-      </c>
-      <c r="N28" s="61"/>
-      <c r="O28" s="61"/>
-      <c r="P28" s="62"/>
+      <c r="M28" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="34"/>
     </row>
     <row r="29" spans="1:17">
-      <c r="A29" s="17">
+      <c r="A29" s="15">
         <v>46190</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="37"/>
       <c r="F29" s="7">
         <v>1</v>
       </c>
-      <c r="G29" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>229</v>
-      </c>
-      <c r="L29" s="60"/>
-      <c r="M29" s="61"/>
-      <c r="N29" s="61"/>
-      <c r="O29" s="61"/>
-      <c r="P29" s="62"/>
+      <c r="G29" s="84" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>225</v>
+      </c>
+      <c r="L29" s="31"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="34"/>
     </row>
     <row r="30" spans="1:17">
-      <c r="A30" s="17">
+      <c r="A30" s="15">
         <v>46190</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="35" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
+      <c r="D30" s="36"/>
+      <c r="E30" s="37"/>
       <c r="F30" s="7">
         <v>1</v>
       </c>
-      <c r="G30" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="L30" s="60" t="s">
+      <c r="G30" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="L30" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="M30" s="58" t="s">
-        <v>290</v>
-      </c>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="62"/>
+      <c r="M30" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="34"/>
     </row>
     <row r="31" spans="1:17" ht="15" thickBot="1">
-      <c r="A31" s="19">
+      <c r="A31" s="17">
         <v>46191</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="51" t="s">
+      <c r="C31" s="38" t="s">
         <v>79</v>
       </c>
-      <c r="D31" s="52"/>
-      <c r="E31" s="53"/>
-      <c r="F31" s="9">
+      <c r="D31" s="39"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="8">
         <v>1</v>
       </c>
-      <c r="G31" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>232</v>
-      </c>
-      <c r="L31" s="78"/>
-      <c r="M31" s="64"/>
-      <c r="N31" s="64"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="65"/>
+      <c r="G31" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="L31" s="43"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="41"/>
+      <c r="P31" s="42"/>
     </row>
     <row r="32" spans="1:17" ht="15" thickBot="1">
-      <c r="A32" s="19">
+      <c r="A32" s="17">
         <v>46191</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="38" t="s">
         <v>80</v>
       </c>
-      <c r="D32" s="52"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="9">
+      <c r="D32" s="39"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="8">
         <v>2</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H32" s="20" t="s">
-        <v>233</v>
+      <c r="G32" s="85" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="18" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:16" ht="18.5">
-      <c r="A33" s="72"/>
-      <c r="B33" s="73"/>
-      <c r="C33" s="73"/>
-      <c r="D33" s="73"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="74"/>
-      <c r="L33" s="66" t="s">
+      <c r="A33" s="52"/>
+      <c r="B33" s="53"/>
+      <c r="C33" s="53"/>
+      <c r="D33" s="53"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="53"/>
+      <c r="G33" s="53"/>
+      <c r="H33" s="54"/>
+      <c r="L33" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="68"/>
+      <c r="M33" s="46"/>
+      <c r="N33" s="46"/>
+      <c r="O33" s="46"/>
+      <c r="P33" s="47"/>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" s="19">
+      <c r="A34" s="17">
         <v>46191</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="51" t="s">
+      <c r="C34" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="D34" s="52"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="9" t="s">
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="H34" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="L34" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="M34" s="61"/>
-      <c r="N34" s="61"/>
-      <c r="O34" s="61"/>
-      <c r="P34" s="62"/>
+      <c r="G34" s="85" t="s">
+        <v>235</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>200</v>
+      </c>
+      <c r="L34" s="31" t="s">
+        <v>231</v>
+      </c>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="34"/>
     </row>
     <row r="35" spans="1:16" ht="15" thickBot="1">
-      <c r="A35" s="19">
+      <c r="A35" s="17">
         <v>46191</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C35" s="51" t="s">
+      <c r="C35" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="52"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="9" t="s">
+      <c r="D35" s="39"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G35" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H35" s="20" t="s">
-        <v>239</v>
-      </c>
-      <c r="L35" s="63"/>
-      <c r="M35" s="64"/>
-      <c r="N35" s="64"/>
-      <c r="O35" s="64"/>
-      <c r="P35" s="65"/>
+      <c r="G35" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="H35" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="L35" s="48"/>
+      <c r="M35" s="41"/>
+      <c r="N35" s="41"/>
+      <c r="O35" s="41"/>
+      <c r="P35" s="42"/>
     </row>
     <row r="36" spans="1:16" ht="15" thickBot="1">
-      <c r="A36" s="17">
+      <c r="A36" s="15">
         <v>46192</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="D36" s="49"/>
-      <c r="E36" s="50"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="37"/>
       <c r="F36" s="7">
         <v>1</v>
       </c>
-      <c r="G36" s="8" t="s">
+      <c r="G36" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H36" s="18" t="s">
-        <v>241</v>
+      <c r="H36" s="16" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="18.5">
-      <c r="A37" s="17">
+      <c r="A37" s="15">
         <v>46192</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="D37" s="49"/>
-      <c r="E37" s="50"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="37"/>
       <c r="F37" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G37" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="H37" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="L37" s="66" t="s">
+      <c r="G37" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="L37" s="45" t="s">
         <v>86</v>
       </c>
-      <c r="M37" s="67"/>
-      <c r="N37" s="67"/>
-      <c r="O37" s="67"/>
-      <c r="P37" s="68"/>
+      <c r="M37" s="46"/>
+      <c r="N37" s="46"/>
+      <c r="O37" s="46"/>
+      <c r="P37" s="47"/>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" s="17">
+      <c r="A38" s="15">
         <v>46192</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="48" t="s">
+      <c r="C38" s="35" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="49"/>
-      <c r="E38" s="50"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="37"/>
       <c r="F38" s="7">
         <v>1</v>
       </c>
-      <c r="G38" s="8" t="s">
+      <c r="G38" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H38" s="18" t="s">
-        <v>242</v>
-      </c>
-      <c r="L38" s="60" t="s">
+      <c r="H38" s="16" t="s">
         <v>237</v>
       </c>
-      <c r="M38" s="61"/>
-      <c r="N38" s="61"/>
-      <c r="O38" s="61"/>
-      <c r="P38" s="62"/>
+      <c r="L38" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="M38" s="33"/>
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="34"/>
     </row>
     <row r="39" spans="1:16" ht="15" thickBot="1">
-      <c r="A39" s="19">
+      <c r="A39" s="17">
         <v>46193</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C39" s="51" t="s">
+      <c r="C39" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="52"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="9" t="s">
+      <c r="D39" s="39"/>
+      <c r="E39" s="40"/>
+      <c r="F39" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G39" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="H39" s="20" t="s">
-        <v>244</v>
-      </c>
-      <c r="L39" s="63"/>
-      <c r="M39" s="64"/>
-      <c r="N39" s="64"/>
-      <c r="O39" s="64"/>
-      <c r="P39" s="65"/>
+      <c r="G39" s="85" t="s">
+        <v>285</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="L39" s="48"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="41"/>
+      <c r="O39" s="41"/>
+      <c r="P39" s="42"/>
     </row>
     <row r="40" spans="1:16" ht="15" thickBot="1">
-      <c r="A40" s="19">
+      <c r="A40" s="17">
         <v>46193</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="52"/>
-      <c r="E40" s="53"/>
-      <c r="F40" s="9">
+      <c r="D40" s="39"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="8">
         <v>1</v>
       </c>
-      <c r="G40" s="10" t="s">
-        <v>218</v>
-      </c>
-      <c r="H40" s="20" t="s">
-        <v>245</v>
+      <c r="G40" s="85" t="s">
+        <v>215</v>
+      </c>
+      <c r="H40" s="18" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="18.5">
-      <c r="A41" s="19">
+      <c r="A41" s="17">
         <v>46193</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="52"/>
-      <c r="E41" s="53"/>
-      <c r="F41" s="9">
+      <c r="D41" s="39"/>
+      <c r="E41" s="40"/>
+      <c r="F41" s="8">
         <v>1</v>
       </c>
-      <c r="G41" s="10" t="s">
+      <c r="G41" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="H41" s="20" t="s">
-        <v>246</v>
-      </c>
-      <c r="L41" s="66" t="s">
+      <c r="H41" s="18" t="s">
+        <v>240</v>
+      </c>
+      <c r="L41" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="M41" s="67"/>
-      <c r="N41" s="67"/>
-      <c r="O41" s="67"/>
-      <c r="P41" s="68"/>
+      <c r="M41" s="46"/>
+      <c r="N41" s="46"/>
+      <c r="O41" s="46"/>
+      <c r="P41" s="47"/>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" s="19">
+      <c r="A42" s="17">
         <v>46193</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="D42" s="52"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="9">
+      <c r="D42" s="39"/>
+      <c r="E42" s="40"/>
+      <c r="F42" s="8">
         <v>1</v>
       </c>
-      <c r="G42" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H42" s="20" t="s">
-        <v>247</v>
-      </c>
-      <c r="L42" s="60" t="s">
-        <v>235</v>
-      </c>
-      <c r="M42" s="61"/>
-      <c r="N42" s="61"/>
-      <c r="O42" s="61"/>
-      <c r="P42" s="62"/>
+      <c r="G42" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="L42" s="31" t="s">
+        <v>230</v>
+      </c>
+      <c r="M42" s="33"/>
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="34"/>
     </row>
     <row r="43" spans="1:16" ht="15" thickBot="1">
-      <c r="A43" s="19">
+      <c r="A43" s="17">
         <v>46193</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C43" s="51" t="s">
+      <c r="C43" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="D43" s="52"/>
-      <c r="E43" s="53"/>
-      <c r="F43" s="9">
+      <c r="D43" s="39"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="8">
         <v>1</v>
       </c>
-      <c r="G43" s="10" t="s">
+      <c r="G43" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="H43" s="20" t="s">
-        <v>248</v>
-      </c>
-      <c r="L43" s="63"/>
-      <c r="M43" s="64"/>
-      <c r="N43" s="64"/>
-      <c r="O43" s="64"/>
-      <c r="P43" s="65"/>
+      <c r="H43" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="L43" s="48"/>
+      <c r="M43" s="41"/>
+      <c r="N43" s="41"/>
+      <c r="O43" s="41"/>
+      <c r="P43" s="42"/>
     </row>
     <row r="44" spans="1:16" ht="15" thickBot="1">
-      <c r="A44" s="17">
+      <c r="A44" s="15">
         <v>46194</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C44" s="48" t="s">
+      <c r="C44" s="35" t="s">
         <v>94</v>
       </c>
-      <c r="D44" s="49"/>
-      <c r="E44" s="50"/>
+      <c r="D44" s="36"/>
+      <c r="E44" s="37"/>
       <c r="F44" s="7">
         <v>1</v>
       </c>
-      <c r="G44" s="8" t="s">
+      <c r="G44" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="H44" s="18" t="s">
-        <v>249</v>
+      <c r="H44" s="16" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="45" spans="1:16" ht="18.5">
-      <c r="A45" s="17">
+      <c r="A45" s="15">
         <v>46194</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C45" s="48" t="s">
+      <c r="C45" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D45" s="49"/>
-      <c r="E45" s="50"/>
+      <c r="D45" s="36"/>
+      <c r="E45" s="37"/>
       <c r="F45" s="7">
         <v>2</v>
       </c>
-      <c r="G45" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>250</v>
-      </c>
-      <c r="L45" s="66" t="s">
+      <c r="G45" s="84" t="s">
+        <v>202</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="L45" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="M45" s="67"/>
-      <c r="N45" s="67"/>
-      <c r="O45" s="67"/>
-      <c r="P45" s="68"/>
+      <c r="M45" s="46"/>
+      <c r="N45" s="46"/>
+      <c r="O45" s="46"/>
+      <c r="P45" s="47"/>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" s="17">
+      <c r="A46" s="15">
         <v>46194</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C46" s="48" t="s">
+      <c r="C46" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D46" s="49"/>
-      <c r="E46" s="50"/>
+      <c r="D46" s="36"/>
+      <c r="E46" s="37"/>
       <c r="F46" s="7">
         <v>1</v>
       </c>
-      <c r="G46" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="L46" s="60" t="s">
-        <v>288</v>
-      </c>
-      <c r="M46" s="61"/>
-      <c r="N46" s="61"/>
-      <c r="O46" s="61"/>
-      <c r="P46" s="62"/>
+      <c r="G46" s="84" t="s">
+        <v>245</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="L46" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="M46" s="33"/>
+      <c r="N46" s="33"/>
+      <c r="O46" s="33"/>
+      <c r="P46" s="34"/>
     </row>
     <row r="47" spans="1:16" ht="15" thickBot="1">
-      <c r="A47" s="17">
+      <c r="A47" s="15">
         <v>46194</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C47" s="48" t="s">
+      <c r="C47" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="50"/>
+      <c r="D47" s="36"/>
+      <c r="E47" s="37"/>
       <c r="F47" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G47" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H47" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="L47" s="63"/>
-      <c r="M47" s="64"/>
-      <c r="N47" s="64"/>
-      <c r="O47" s="64"/>
-      <c r="P47" s="65"/>
+      <c r="G47" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="L47" s="48"/>
+      <c r="M47" s="41"/>
+      <c r="N47" s="41"/>
+      <c r="O47" s="41"/>
+      <c r="P47" s="42"/>
     </row>
     <row r="48" spans="1:16" ht="15" thickBot="1">
-      <c r="A48" s="19">
+      <c r="A48" s="17">
         <v>46195</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="D48" s="52"/>
-      <c r="E48" s="53"/>
-      <c r="F48" s="9">
+      <c r="D48" s="39"/>
+      <c r="E48" s="40"/>
+      <c r="F48" s="8">
         <v>1</v>
       </c>
-      <c r="G48" s="10" t="s">
+      <c r="G48" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="H48" s="20" t="s">
-        <v>254</v>
+      <c r="H48" s="18" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="18.5">
-      <c r="A49" s="19">
+      <c r="A49" s="17">
         <v>46195</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="D49" s="52"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="9">
+      <c r="D49" s="39"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="8">
         <v>2</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H49" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="L49" s="66" t="s">
+      <c r="G49" s="85" t="s">
+        <v>219</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="L49" s="45" t="s">
         <v>101</v>
       </c>
-      <c r="M49" s="67"/>
-      <c r="N49" s="67"/>
-      <c r="O49" s="67"/>
-      <c r="P49" s="68"/>
+      <c r="M49" s="46"/>
+      <c r="N49" s="46"/>
+      <c r="O49" s="46"/>
+      <c r="P49" s="47"/>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" s="19">
+      <c r="A50" s="17">
         <v>46195</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="D50" s="52"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="9">
+      <c r="D50" s="39"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="8">
         <v>1</v>
       </c>
-      <c r="G50" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="L50" s="60" t="s">
-        <v>237</v>
-      </c>
-      <c r="M50" s="61"/>
-      <c r="N50" s="61"/>
-      <c r="O50" s="61"/>
-      <c r="P50" s="62"/>
+      <c r="G50" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>249</v>
+      </c>
+      <c r="L50" s="31" t="s">
+        <v>232</v>
+      </c>
+      <c r="M50" s="33"/>
+      <c r="N50" s="33"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="34"/>
     </row>
     <row r="51" spans="1:16" ht="15" thickBot="1">
-      <c r="A51" s="19">
+      <c r="A51" s="17">
         <v>46195</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="52"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="9">
+      <c r="D51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="8">
         <v>1</v>
       </c>
-      <c r="G51" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="H51" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="L51" s="63"/>
-      <c r="M51" s="64"/>
-      <c r="N51" s="64"/>
-      <c r="O51" s="64"/>
-      <c r="P51" s="65"/>
+      <c r="G51" s="85" t="s">
+        <v>245</v>
+      </c>
+      <c r="H51" s="18" t="s">
+        <v>250</v>
+      </c>
+      <c r="L51" s="48"/>
+      <c r="M51" s="41"/>
+      <c r="N51" s="41"/>
+      <c r="O51" s="41"/>
+      <c r="P51" s="42"/>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" s="17">
+      <c r="A52" s="15">
         <v>46196</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C52" s="48" t="s">
+      <c r="C52" s="35" t="s">
         <v>104</v>
       </c>
-      <c r="D52" s="49"/>
-      <c r="E52" s="50"/>
+      <c r="D52" s="36"/>
+      <c r="E52" s="37"/>
       <c r="F52" s="7">
         <v>1</v>
       </c>
-      <c r="G52" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>226</v>
+      <c r="G52" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="H52" s="16" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" s="17">
+      <c r="A53" s="15">
         <v>46196</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="48" t="s">
+      <c r="C53" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D53" s="49"/>
-      <c r="E53" s="50"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="37"/>
       <c r="F53" s="7">
         <v>2</v>
       </c>
-      <c r="G53" s="8" t="s">
-        <v>257</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>258</v>
+      <c r="G53" s="84" t="s">
+        <v>202</v>
+      </c>
+      <c r="H53" s="16" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" s="17">
+      <c r="A54" s="15">
         <v>46196</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C54" s="48" t="s">
+      <c r="C54" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D54" s="49"/>
-      <c r="E54" s="50"/>
+      <c r="D54" s="36"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="7">
         <v>1</v>
       </c>
-      <c r="G54" s="8" t="s">
-        <v>259</v>
-      </c>
-      <c r="H54" s="18" t="s">
-        <v>260</v>
+      <c r="G54" s="84" t="s">
+        <v>197</v>
+      </c>
+      <c r="H54" s="16" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" s="17">
+      <c r="A55" s="15">
         <v>46196</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C55" s="48" t="s">
+      <c r="C55" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="D55" s="49"/>
-      <c r="E55" s="50"/>
+      <c r="D55" s="36"/>
+      <c r="E55" s="37"/>
       <c r="F55" s="7">
         <v>1</v>
       </c>
-      <c r="G55" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>231</v>
+      <c r="G55" s="84" t="s">
+        <v>283</v>
+      </c>
+      <c r="H55" s="16" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" s="19">
+      <c r="A56" s="17">
         <v>46197</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C56" s="51" t="s">
+      <c r="C56" s="38" t="s">
         <v>108</v>
       </c>
-      <c r="D56" s="52"/>
-      <c r="E56" s="53"/>
-      <c r="F56" s="9" t="s">
+      <c r="D56" s="39"/>
+      <c r="E56" s="40"/>
+      <c r="F56" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="H56" s="20" t="s">
-        <v>261</v>
+      <c r="G56" s="85" t="s">
+        <v>281</v>
+      </c>
+      <c r="H56" s="18" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" s="19">
+      <c r="A57" s="17">
         <v>46197</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C57" s="51" t="s">
+      <c r="C57" s="38" t="s">
         <v>109</v>
       </c>
-      <c r="D57" s="52"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="9">
+      <c r="D57" s="39"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="8">
         <v>1</v>
       </c>
-      <c r="G57" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H57" s="20" t="s">
-        <v>262</v>
+      <c r="G57" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" s="69"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="70"/>
-      <c r="D58" s="70"/>
-      <c r="E58" s="70"/>
-      <c r="F58" s="70"/>
-      <c r="G58" s="70"/>
-      <c r="H58" s="71"/>
+      <c r="A58" s="55"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="56"/>
+      <c r="G58" s="56"/>
+      <c r="H58" s="57"/>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" s="19">
+      <c r="A59" s="17">
         <v>46197</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C59" s="51" t="s">
+      <c r="C59" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="D59" s="52"/>
-      <c r="E59" s="53"/>
-      <c r="F59" s="9">
+      <c r="D59" s="39"/>
+      <c r="E59" s="40"/>
+      <c r="F59" s="8">
         <v>1</v>
       </c>
-      <c r="G59" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="H59" s="20" t="s">
-        <v>274</v>
+      <c r="G59" s="85" t="s">
+        <v>204</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" s="19">
+      <c r="A60" s="17">
         <v>46197</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="C60" s="51" t="s">
+      <c r="C60" s="38" t="s">
         <v>111</v>
       </c>
-      <c r="D60" s="52"/>
-      <c r="E60" s="53"/>
-      <c r="F60" s="9">
+      <c r="D60" s="39"/>
+      <c r="E60" s="40"/>
+      <c r="F60" s="8">
         <v>1</v>
       </c>
-      <c r="G60" s="10" t="s">
+      <c r="G60" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="H60" s="20" t="s">
-        <v>271</v>
+      <c r="H60" s="18" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" s="17">
+      <c r="A61" s="15">
         <v>46198</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C61" s="48" t="s">
+      <c r="C61" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="D61" s="49"/>
-      <c r="E61" s="50"/>
+      <c r="D61" s="36"/>
+      <c r="E61" s="37"/>
       <c r="F61" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G61" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>272</v>
+      <c r="G61" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H61" s="16" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" s="17">
+      <c r="A62" s="15">
         <v>46198</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C62" s="48" t="s">
+      <c r="C62" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50"/>
+      <c r="D62" s="36"/>
+      <c r="E62" s="37"/>
       <c r="F62" s="7">
         <v>1</v>
       </c>
-      <c r="G62" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>268</v>
+      <c r="G62" s="84" t="s">
+        <v>245</v>
+      </c>
+      <c r="H62" s="16" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" s="17">
+      <c r="A63" s="15">
         <v>46198</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C63" s="48" t="s">
+      <c r="C63" s="35" t="s">
         <v>114</v>
       </c>
-      <c r="D63" s="49"/>
-      <c r="E63" s="50"/>
+      <c r="D63" s="36"/>
+      <c r="E63" s="37"/>
       <c r="F63" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G63" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>273</v>
+      <c r="G63" s="84" t="s">
+        <v>282</v>
+      </c>
+      <c r="H63" s="16" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" s="17">
+      <c r="A64" s="15">
         <v>46198</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C64" s="48" t="s">
+      <c r="C64" s="35" t="s">
         <v>115</v>
       </c>
-      <c r="D64" s="49"/>
-      <c r="E64" s="50"/>
+      <c r="D64" s="36"/>
+      <c r="E64" s="37"/>
       <c r="F64" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G64" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H64" s="18" t="s">
-        <v>277</v>
+      <c r="G64" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H64" s="16" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="17">
+      <c r="A65" s="15">
         <v>46198</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C65" s="48" t="s">
+      <c r="C65" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="D65" s="49"/>
-      <c r="E65" s="50"/>
+      <c r="D65" s="36"/>
+      <c r="E65" s="37"/>
       <c r="F65" s="7">
         <v>1</v>
       </c>
-      <c r="G65" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>276</v>
+      <c r="G65" s="84" t="s">
+        <v>204</v>
+      </c>
+      <c r="H65" s="16" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="17">
+      <c r="A66" s="15">
         <v>46198</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C66" s="48" t="s">
+      <c r="C66" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="D66" s="49"/>
-      <c r="E66" s="50"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="37"/>
       <c r="F66" s="7">
         <v>2</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>275</v>
+      <c r="G66" s="84" t="s">
+        <v>206</v>
+      </c>
+      <c r="H66" s="16" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="19">
+      <c r="A67" s="17">
         <v>46199</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C67" s="51" t="s">
+      <c r="C67" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="D67" s="52"/>
-      <c r="E67" s="53"/>
-      <c r="F67" s="9">
+      <c r="D67" s="39"/>
+      <c r="E67" s="40"/>
+      <c r="F67" s="8">
         <v>2</v>
       </c>
-      <c r="G67" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H67" s="20" t="s">
-        <v>247</v>
+      <c r="G67" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="H67" s="18" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="19">
+      <c r="A68" s="17">
         <v>46199</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C68" s="51" t="s">
+      <c r="C68" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="D68" s="52"/>
-      <c r="E68" s="53"/>
-      <c r="F68" s="9">
+      <c r="D68" s="39"/>
+      <c r="E68" s="40"/>
+      <c r="F68" s="8">
         <v>1</v>
       </c>
-      <c r="G68" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H68" s="20" t="s">
-        <v>278</v>
+      <c r="G68" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H68" s="18" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="19">
+      <c r="A69" s="17">
         <v>46199</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C69" s="51" t="s">
+      <c r="C69" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D69" s="52"/>
-      <c r="E69" s="53"/>
-      <c r="F69" s="9">
+      <c r="D69" s="39"/>
+      <c r="E69" s="40"/>
+      <c r="F69" s="8">
         <v>2</v>
       </c>
-      <c r="G69" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="H69" s="20" t="s">
-        <v>279</v>
+      <c r="G69" s="85" t="s">
+        <v>219</v>
+      </c>
+      <c r="H69" s="18" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="70" spans="1:8">
-      <c r="A70" s="19">
+      <c r="A70" s="17">
         <v>46199</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C70" s="51" t="s">
+      <c r="C70" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="D70" s="52"/>
-      <c r="E70" s="53"/>
-      <c r="F70" s="9">
+      <c r="D70" s="39"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="8">
         <v>1</v>
       </c>
-      <c r="G70" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="H70" s="20" t="s">
-        <v>280</v>
+      <c r="G70" s="85" t="s">
+        <v>286</v>
+      </c>
+      <c r="H70" s="18" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="71" spans="1:8">
-      <c r="A71" s="19">
+      <c r="A71" s="17">
         <v>46199</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C71" s="51" t="s">
+      <c r="C71" s="38" t="s">
         <v>122</v>
       </c>
-      <c r="D71" s="52"/>
-      <c r="E71" s="53"/>
-      <c r="F71" s="9">
+      <c r="D71" s="39"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="8">
         <v>2</v>
       </c>
-      <c r="G71" s="25" t="s">
-        <v>266</v>
-      </c>
-      <c r="H71" s="20" t="s">
-        <v>225</v>
+      <c r="G71" s="85" t="s">
+        <v>287</v>
+      </c>
+      <c r="H71" s="18" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="72" spans="1:8">
-      <c r="A72" s="19">
+      <c r="A72" s="17">
         <v>46199</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C72" s="51" t="s">
+      <c r="C72" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="D72" s="52"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="9">
+      <c r="D72" s="39"/>
+      <c r="E72" s="40"/>
+      <c r="F72" s="8">
         <v>1</v>
       </c>
-      <c r="G72" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="H72" s="20" t="s">
-        <v>281</v>
+      <c r="G72" s="85" t="s">
+        <v>283</v>
+      </c>
+      <c r="H72" s="18" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="73" spans="1:8">
-      <c r="A73" s="17">
+      <c r="A73" s="15">
         <v>46200</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C73" s="48" t="s">
+      <c r="C73" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="D73" s="49"/>
-      <c r="E73" s="50"/>
+      <c r="D73" s="36"/>
+      <c r="E73" s="37"/>
       <c r="F73" s="7">
         <v>2</v>
       </c>
-      <c r="G73" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H73" s="18" t="s">
-        <v>267</v>
+      <c r="G73" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="74" spans="1:8">
-      <c r="A74" s="17">
+      <c r="A74" s="15">
         <v>46200</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C74" s="48" t="s">
+      <c r="C74" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D74" s="49"/>
-      <c r="E74" s="50"/>
+      <c r="D74" s="36"/>
+      <c r="E74" s="37"/>
       <c r="F74" s="7">
         <v>2</v>
       </c>
-      <c r="G74" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H74" s="18" t="s">
-        <v>282</v>
+      <c r="G74" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="H74" s="16" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="75" spans="1:8">
-      <c r="A75" s="17">
+      <c r="A75" s="15">
         <v>46200</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C75" s="48" t="s">
+      <c r="C75" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="D75" s="49"/>
-      <c r="E75" s="50"/>
+      <c r="D75" s="36"/>
+      <c r="E75" s="37"/>
       <c r="F75" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G75" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="H75" s="18" t="s">
-        <v>283</v>
+      <c r="G75" s="84" t="s">
+        <v>281</v>
+      </c>
+      <c r="H75" s="16" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="76" spans="1:8">
-      <c r="A76" s="17">
+      <c r="A76" s="15">
         <v>46200</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C76" s="48" t="s">
+      <c r="C76" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="D76" s="49"/>
-      <c r="E76" s="50"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="37"/>
       <c r="F76" s="7">
         <v>2</v>
       </c>
-      <c r="G76" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H76" s="18" t="s">
-        <v>270</v>
+      <c r="G76" s="84" t="s">
+        <v>206</v>
+      </c>
+      <c r="H76" s="16" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="77" spans="1:8">
-      <c r="A77" s="17">
+      <c r="A77" s="15">
         <v>46200</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C77" s="48" t="s">
+      <c r="C77" s="35" t="s">
         <v>128</v>
       </c>
-      <c r="D77" s="49"/>
-      <c r="E77" s="50"/>
+      <c r="D77" s="36"/>
+      <c r="E77" s="37"/>
       <c r="F77" s="7">
         <v>2</v>
       </c>
-      <c r="G77" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H77" s="18" t="s">
-        <v>269</v>
+      <c r="G77" s="84" t="s">
+        <v>219</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="78" spans="1:8">
-      <c r="A78" s="17">
+      <c r="A78" s="15">
         <v>46200</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C78" s="48" t="s">
+      <c r="C78" s="35" t="s">
         <v>129</v>
       </c>
-      <c r="D78" s="49"/>
-      <c r="E78" s="50"/>
+      <c r="D78" s="36"/>
+      <c r="E78" s="37"/>
       <c r="F78" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="G78" s="26" t="s">
-        <v>207</v>
-      </c>
-      <c r="H78" s="18" t="s">
-        <v>284</v>
+      <c r="G78" s="84" t="s">
+        <v>282</v>
+      </c>
+      <c r="H78" s="16" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="79" spans="1:8">
-      <c r="A79" s="19">
+      <c r="A79" s="17">
         <v>46201</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C79" s="51" t="s">
+      <c r="C79" s="38" t="s">
         <v>130</v>
       </c>
-      <c r="D79" s="52"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="9" t="s">
+      <c r="D79" s="39"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="G79" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="H79" s="20" t="s">
-        <v>285</v>
+      <c r="G79" s="85" t="s">
+        <v>282</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="80" spans="1:8">
-      <c r="A80" s="19">
+      <c r="A80" s="17">
         <v>46201</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C80" s="51" t="s">
+      <c r="C80" s="38" t="s">
         <v>131</v>
       </c>
-      <c r="D80" s="52"/>
-      <c r="E80" s="53"/>
-      <c r="F80" s="9">
+      <c r="D80" s="39"/>
+      <c r="E80" s="40"/>
+      <c r="F80" s="8">
         <v>2</v>
       </c>
-      <c r="G80" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="H80" s="20" t="s">
-        <v>286</v>
+      <c r="G80" s="85" t="s">
+        <v>202</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:8">
-      <c r="A81" s="19">
+      <c r="A81" s="17">
         <v>46201</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C81" s="51" t="s">
+      <c r="C81" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="D81" s="52"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="9">
+      <c r="D81" s="39"/>
+      <c r="E81" s="40"/>
+      <c r="F81" s="8">
         <v>2</v>
       </c>
-      <c r="G81" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="H81" s="20" t="s">
-        <v>227</v>
+      <c r="G81" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="82" spans="1:8" ht="15" thickBot="1">
-      <c r="A82" s="21">
+      <c r="A82" s="19">
         <v>46201</v>
       </c>
-      <c r="B82" s="22" t="s">
+      <c r="B82" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C82" s="54" t="s">
+      <c r="C82" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="D82" s="55"/>
-      <c r="E82" s="56"/>
-      <c r="F82" s="23" t="s">
+      <c r="D82" s="61"/>
+      <c r="E82" s="62"/>
+      <c r="F82" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="G82" s="88" t="s">
-        <v>200</v>
-      </c>
-      <c r="H82" s="24" t="s">
-        <v>287</v>
+      <c r="G82" s="86" t="s">
+        <v>281</v>
+      </c>
+      <c r="H82" s="22" t="s">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="139">
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="L42:P43"/>
+    <mergeCell ref="L45:P45"/>
+    <mergeCell ref="L46:P47"/>
+    <mergeCell ref="L49:P49"/>
+    <mergeCell ref="L50:P51"/>
+    <mergeCell ref="A58:H58"/>
+    <mergeCell ref="L33:P33"/>
+    <mergeCell ref="L34:P35"/>
+    <mergeCell ref="L37:P37"/>
+    <mergeCell ref="L38:P39"/>
+    <mergeCell ref="L41:P41"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P25"/>
+    <mergeCell ref="L27:P27"/>
+    <mergeCell ref="L28:L29"/>
+    <mergeCell ref="L30:L31"/>
+    <mergeCell ref="M28:P29"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="M30:P31"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="O13:Q13"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="O14:Q14"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
     <mergeCell ref="A5:T6"/>
     <mergeCell ref="C8:E8"/>
     <mergeCell ref="J8:Q8"/>
@@ -4945,200 +5035,85 @@
     <mergeCell ref="O9:Q9"/>
     <mergeCell ref="J10:K10"/>
     <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="O13:Q13"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="O14:Q14"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="L23:P23"/>
-    <mergeCell ref="L24:P25"/>
-    <mergeCell ref="L27:P27"/>
-    <mergeCell ref="L28:L29"/>
-    <mergeCell ref="L30:L31"/>
-    <mergeCell ref="M28:P29"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="M30:P31"/>
-    <mergeCell ref="L33:P33"/>
-    <mergeCell ref="L34:P35"/>
-    <mergeCell ref="L37:P37"/>
-    <mergeCell ref="L38:P39"/>
-    <mergeCell ref="L41:P41"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="L42:P43"/>
-    <mergeCell ref="L45:P45"/>
-    <mergeCell ref="L46:P47"/>
-    <mergeCell ref="L49:P49"/>
-    <mergeCell ref="L50:P51"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="13">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$4:$A$7</xm:f>
           </x14:formula1>
           <xm:sqref>L10:Q10</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$9:$A$12</xm:f>
           </x14:formula1>
           <xm:sqref>L11:Q11</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000002000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$14:$A$17</xm:f>
           </x14:formula1>
           <xm:sqref>L12:Q12</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000003000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$19:$A$22</xm:f>
           </x14:formula1>
           <xm:sqref>L13:Q13</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000004000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$24:$A$27</xm:f>
           </x14:formula1>
           <xm:sqref>L14:Q14</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000005000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$29:$A$32</xm:f>
           </x14:formula1>
           <xm:sqref>L15:Q15</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000006000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$34:$A$37</xm:f>
           </x14:formula1>
           <xm:sqref>L16:Q16</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000007000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$39:$A$42</xm:f>
           </x14:formula1>
           <xm:sqref>L17:Q17</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000008000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$44:$A$47</xm:f>
           </x14:formula1>
           <xm:sqref>L18:Q18</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000009000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$49:$A$52</xm:f>
           </x14:formula1>
           <xm:sqref>L19:Q19</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000A000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$54:$A$57</xm:f>
           </x14:formula1>
           <xm:sqref>L20:Q20</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000B000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$59:$A$62</xm:f>
           </x14:formula1>
           <xm:sqref>L21:Q21</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-00000C000000}">
           <x14:formula1>
             <xm:f>Gironi!$A$78:$A$80</xm:f>
           </x14:formula1>
@@ -5151,7 +5126,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:A80"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
@@ -5159,327 +5134,327 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:1">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="10" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:1">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:1">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="11" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="11" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="11" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="11" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="11" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="11" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="11" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:1">
-      <c r="A23" s="12" t="s">
+      <c r="A23" s="10" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="11" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="11" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="11" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="27" spans="1:1">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="11" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="11" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="30" spans="1:1">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="11" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="11" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="11" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" s="12" t="s">
+      <c r="A33" s="10" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="11" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="11" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="11" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:1">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="11" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="12" t="s">
+      <c r="A38" s="10" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="11" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" s="13" t="s">
+      <c r="A40" s="11" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="41" spans="1:1">
-      <c r="A41" s="13" t="s">
+      <c r="A41" s="11" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="13" t="s">
+      <c r="A42" s="11" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" s="12" t="s">
+      <c r="A43" s="10" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" s="13" t="s">
+      <c r="A44" s="11" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="13" t="s">
+      <c r="A45" s="11" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="13" t="s">
+      <c r="A46" s="11" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="13" t="s">
+      <c r="A47" s="11" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="12" t="s">
+      <c r="A48" s="10" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="13" t="s">
+      <c r="A49" s="11" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="13" t="s">
+      <c r="A50" s="11" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="11" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" s="13" t="s">
+      <c r="A52" s="11" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" s="12" t="s">
+      <c r="A53" s="10" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="54" spans="1:1">
-      <c r="A54" s="13" t="s">
+      <c r="A54" s="11" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="11" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="11" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" s="13" t="s">
+      <c r="A57" s="11" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" s="12" t="s">
+      <c r="A58" s="10" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" s="13" t="s">
+      <c r="A59" s="11" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" s="13" t="s">
+      <c r="A60" s="11" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="61" spans="1:1">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="11" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="13" t="s">
+      <c r="A62" s="11" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" s="12" t="s">
+      <c r="A63" s="10" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="78" spans="1:1">
-      <c r="A78" s="14">
+      <c r="A78" s="12">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="14" t="s">
+      <c r="A79" s="12" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" s="14">
+      <c r="A80" s="12">
         <v>2</v>
       </c>
     </row>
